--- a/artfynd/A 66443-2021 artfynd.xlsx
+++ b/artfynd/A 66443-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66443-2021 artfynd.xlsx
+++ b/artfynd/A 66443-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104314169</v>
+        <v>104314163</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554942.2018652926</v>
+        <v>555053</v>
       </c>
       <c r="R2" t="n">
-        <v>7318503.163864368</v>
+        <v>7318647</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,19 +748,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104314187</v>
+        <v>104314169</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,13 +813,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555019.5673178061</v>
+        <v>554942</v>
       </c>
       <c r="R3" t="n">
-        <v>7318385.219750941</v>
+        <v>7318503</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,19 +846,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104314193</v>
+        <v>104314187</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +886,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,13 +911,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555130.7757946982</v>
+        <v>555020</v>
       </c>
       <c r="R4" t="n">
-        <v>7318353.535211498</v>
+        <v>7318385</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,19 +944,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +973,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104314190</v>
+        <v>104314178</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,24 +984,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,13 +1013,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555085.1560225047</v>
+        <v>555013</v>
       </c>
       <c r="R5" t="n">
-        <v>7318348.983782073</v>
+        <v>7318374</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,19 +1046,9 @@
           <t>2022-10-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,240 +1072,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>104314163</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>353</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dvärgbägarlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cladonia parasitica</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>555053.2658377867</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7318647.567051125</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>104314178</v>
-      </c>
-      <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Sorsele, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>555012.8446915548</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7318374.083471083</v>
-      </c>
-      <c r="S7" t="n">
-        <v>20</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66443-2021 artfynd.xlsx
+++ b/artfynd/A 66443-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104314163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104314169</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104314187</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,8 +1092,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104314178</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>